--- a/public/modelos/modelo-importacao-zarpellon.xlsx
+++ b/public/modelos/modelo-importacao-zarpellon.xlsx
@@ -436,14 +436,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="66" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -467,7 +468,12 @@
           <t>Valor Base</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Valor de Venda</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>COMO PREENCHER (apague esta coluna se quiser):</t>
         </is>
@@ -490,44 +496,68 @@
       <c r="D2" s="5" t="n">
         <v>8.85</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="E2" s="5" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>1. Uma linha por produto, a partir da linha 2.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2. Produto = código da peça na Zarpellon (coluna A).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>3. Descrição = nome/descrição da peça (coluna B).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>4. Qtd. = quantidade comprada. Valor Base = custo unitário (coluna D).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>5. A linha 2 é só um EXEMPLO — apague e coloque os seus itens.</t>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>5. Valor de Venda (coluna E) é OPCIONAL: se preencher, esse é o preço</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>6. Não mexa na linha 1 (cabeçalho).</t>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   de venda do produto. Se deixar em branco, o sistema aplica a regra</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   padrão (custo × 3) — útil só pra quem já precifica na Zarpellon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6. A linha 2 é só um EXEMPLO — apague e coloque os seus itens.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>7. Não mexa na linha 1 (cabeçalho).</t>
         </is>
       </c>
     </row>
